--- a/output/DummyFrench_English.xlsx
+++ b/output/DummyFrench_English.xlsx
@@ -581,18 +581,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iida</t>
+          <t>Ōaza Iida</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -609,18 +609,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iida-Shinden</t>
+          <t>Ōaza Iida-Shinden</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -637,18 +637,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uetaya-hon</t>
+          <t>Ōaza Uetaya-hon</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -665,18 +665,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uetaya-honmura-Shinden</t>
+          <t>Ōaza Uetaya-honmura-Shinden</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -693,18 +693,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uchino-Hongō</t>
+          <t>Ōaza Uchino-Hongō</t>
         </is>
       </c>
       <c r="D9" s="4" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -721,18 +721,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōaza Sashiōgi</t>
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -749,18 +749,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sashiōgi-Ryōtsuji</t>
+          <t>Ōaza Sashiōgi-Ryōtsuji</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -777,18 +777,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sashiōgi-Ryōbessho</t>
+          <t>Ōaza Sashiōgi-Ryōbessho</t>
         </is>
       </c>
       <c r="D12" s="4" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -805,18 +805,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sajikawa</t>
+          <t>Ōaza Sajikawa</t>
         </is>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -833,18 +833,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sanjōmachi</t>
+          <t>Ōaza Sanjōmachi</t>
         </is>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -861,18 +861,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Shimane</t>
+          <t>Ōaza Shimane</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -889,18 +889,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seiganji</t>
+          <t>Ōaza Seiganji</t>
         </is>
       </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -917,18 +917,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Takagi</t>
+          <t>Ōaza Takagi</t>
         </is>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -945,18 +945,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tsukamoto</t>
+          <t>Ōaza Tsukamoto</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>1st chōme</t>
+          <t>1er chōme</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2nd chōme</t>
+          <t>2e chōme</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3rd chōme</t>
+          <t>3e chōme</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1069,18 +1069,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zaza Tsuchiya</t>
+          <t>Ōaza Tsuchiya</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1097,18 +1097,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nakakugi</t>
+          <t>Ōaza Nakakugi</t>
         </is>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1125,18 +1125,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nakanobayashi</t>
+          <t>Ōaza Nakanobayashi</t>
         </is>
       </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1153,18 +1153,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nishi-Asuma</t>
+          <t>Ōaza Nishi-Asuma</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1181,18 +1181,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nishi-Arai</t>
+          <t>Ōaza Nishi-Arai</t>
         </is>
       </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1209,18 +1209,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hirakata-Ryōryōke</t>
+          <t>Ōaza Hirakata-Ryōryōke</t>
         </is>
       </c>
       <c r="D27" s="4" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1237,18 +1237,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Futasumiya</t>
+          <t>Ōaza Futatsumiya</t>
         </is>
       </c>
       <c r="D28" s="4" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1265,18 +1265,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Futasumiya</t>
+          <t>Ōaza Futatsumiya</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1304,7 +1304,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1321,18 +1321,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hōrai</t>
+          <t>Ōaza Hōrai</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1349,18 +1349,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mizuhata</t>
+          <t>Ōaza Mizuhata</t>
         </is>
       </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1377,18 +1377,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minegishi</t>
+          <t>Ōaza Minegishi</t>
         </is>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>5th chōme</t>
+          <t>5e chōme</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>6th chōme</t>
+          <t>6e chōme</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1480,7 +1480,7 @@
       <c r="D36" s="4" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1508,7 +1508,7 @@
       <c r="D37" s="4" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1st chōme</t>
+          <t>1er chōme</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2nd chōme</t>
+          <t>2e chōme</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1589,22 +1589,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nishi-Imiya</t>
+          <t>Nishi-Ōmiya</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1st chōme</t>
+          <t>1er chōme</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -1626,22 +1626,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nishi-Imiya</t>
+          <t>Nishi-Ōmiya</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2nd chōme</t>
+          <t>2e chōme</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1663,22 +1663,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nishi-Imiya</t>
+          <t>Nishi-Ōmiya</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>3rd chōme</t>
+          <t>3e chōme</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saitama-shi, Nishi district</t>
+          <t>Saitama-shi, arrondissement Nishi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nishi-Imiya</t>
+          <t>Nishi-Ōmiya</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>4th chōme</t>
+          <t>4e chōme</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sashiōgi</t>
+          <t>Ōmiya Sashiōgi</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Saitama-shi, Kita district</t>
+          <t>Saitama-shi, arrondissement Kita</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1st chōme</t>
+          <t>1er chōme</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Saitama-shi, Kita district</t>
+          <t>Saitama-shi, arrondissement Kita</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2nd chōme</t>
+          <t>2e chōme</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -1801,22 +1801,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Saitama-shi, Kita district</t>
+          <t>Saitama-shi, arrondissement Kita</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nari-chō</t>
+          <t>Ōnari-chō</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>4th chōme</t>
+          <t>4e chōme</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -1833,18 +1833,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saitama-shi, Kita district</t>
+          <t>Saitama-shi, arrondissement Kita</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kamika</t>
+          <t>Ōaza Kamika</t>
         </is>
       </c>
       <c r="D47" s="4" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Saitama-shi, Kita district</t>
+          <t>Saitama-shi, arrondissement Kita</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2nd chōme</t>
+          <t>2e chōme</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Saitama-shi, Kita district</t>
+          <t>Saitama-shi, arrondissement Kita</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1904,7 +1904,7 @@
       <c r="D49" s="4" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Saitama-shi, Kita district</t>
+          <t>Saitama-shi, arrondissement Kita</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1932,7 +1932,7 @@
       <c r="D50" s="4" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Saitama-shi, Kita district</t>
+          <t>Saitama-shi, arrondissement Kita</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1st chōme</t>
+          <t>1er chōme</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Higashi-</t>
+          <t>Ōmiya Higashi-Ōnari</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
